--- a/CS492_GP3_Sprint2_Week1.xlsx
+++ b/CS492_GP3_Sprint2_Week1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/7A17F28CBDB6A8A9/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="114" documentId="8_{A76A665B-8CE9-419E-A187-8E84A598E366}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3E9BDD80-FC14-4B04-944E-64D71CEC1858}"/>
+  <xr:revisionPtr revIDLastSave="170" documentId="8_{A76A665B-8CE9-419E-A187-8E84A598E366}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C6572F7E-00C8-4D26-86E2-A3354A8B98FE}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sprint 1 - Week 1" sheetId="1" r:id="rId1"/>
@@ -19,10 +19,12 @@
     <sheet name="Hours Log Week-1" sheetId="2" r:id="rId4"/>
     <sheet name="Hours Log Week 2" sheetId="6" r:id="rId5"/>
     <sheet name="Hours Log Week 3" sheetId="10" r:id="rId6"/>
-    <sheet name="Team Communication" sheetId="3" r:id="rId7"/>
-    <sheet name="Sheet4" sheetId="12" r:id="rId8"/>
-    <sheet name="Week 1 Submission Checklist" sheetId="4" r:id="rId9"/>
-    <sheet name="Week 2 Submission Checklist" sheetId="8" r:id="rId10"/>
+    <sheet name="Team Communication Week 1" sheetId="3" r:id="rId7"/>
+    <sheet name="Team Communication Week 2" sheetId="12" r:id="rId8"/>
+    <sheet name="Team Communication Week 3" sheetId="14" r:id="rId9"/>
+    <sheet name="Week 1 Submission Checklist" sheetId="4" r:id="rId10"/>
+    <sheet name="Week 2 Submission Checklist" sheetId="8" r:id="rId11"/>
+    <sheet name="Week 3 Submission Checklist" sheetId="13" r:id="rId12"/>
   </sheets>
   <calcPr calcId="191028" refMode="R1C1" iterateCount="0" calcOnSave="0" concurrentCalc="0"/>
   <extLst>
@@ -45,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="605" uniqueCount="254">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="655" uniqueCount="273">
   <si>
     <t>CS492 Airline Reservation System — Sprint 1, Week 1</t>
   </si>
@@ -817,6 +819,63 @@
   <si>
     <t>Tonya Coyne and Macameron Clark</t>
   </si>
+  <si>
+    <t>Organize a plan for week 2</t>
+  </si>
+  <si>
+    <t>planning</t>
+  </si>
+  <si>
+    <t>progress check</t>
+  </si>
+  <si>
+    <t>Progress Check</t>
+  </si>
+  <si>
+    <t>Email</t>
+  </si>
+  <si>
+    <t>Group Communication Record — Week 3</t>
+  </si>
+  <si>
+    <t>Ricky will start on the API. Tonya will continue to update and document.</t>
+  </si>
+  <si>
+    <t>Melissa and Macameron will be doing testing</t>
+  </si>
+  <si>
+    <t>Week 3 Submission Checklist</t>
+  </si>
+  <si>
+    <t>Communication with the Group: Group members are communicating well through the week.</t>
+  </si>
+  <si>
+    <t>Sprint 2 Planning: Sprint plan updated and refined based on the progress completed in Sprint 1.</t>
+  </si>
+  <si>
+    <t>Sprint 2 – Week 1 Hours tracking: team members recorded hours for Sprint 2 – Week 1</t>
+  </si>
+  <si>
+    <t>Non Development Activities: groups added non development activities to the sprint planning document.</t>
+  </si>
+  <si>
+    <t>see communication log</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Updated Sprint Planning </t>
+  </si>
+  <si>
+    <t>See hours log</t>
+  </si>
+  <si>
+    <t>Check naming, Sprint 2 Week 1 labels, file organization, and relevance.</t>
+  </si>
+  <si>
+    <t>See Sprint Log</t>
+  </si>
+  <si>
+    <t>We are on track</t>
+  </si>
 </sst>
 </file>
 
@@ -827,7 +886,7 @@
     <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="166" formatCode="mm/dd/yy"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -865,6 +924,11 @@
     <font>
       <sz val="8"/>
       <name val="Carlito"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="8">
@@ -973,7 +1037,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1081,16 +1145,7 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1101,13 +1156,25 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1123,6 +1190,99 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>1089754</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>472481</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{25F7482C-244D-DA3B-879A-292DA1A55337}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9829800" y="1973580"/>
+          <a:ext cx="1089754" cy="472481"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>1089754</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>472481</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Picture 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1273FC17-E0A0-A7FB-627C-87AD636B9216}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9829800" y="2484120"/>
+          <a:ext cx="1089754" cy="472481"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1342,26 +1502,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" s="7" customFormat="1" ht="30" customHeight="1">
-      <c r="A1" s="42" t="s">
+      <c r="A1" s="40" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="42"/>
-      <c r="C1" s="42"/>
-      <c r="D1" s="42"/>
-      <c r="E1" s="42"/>
-      <c r="F1" s="42"/>
-      <c r="G1" s="42"/>
-      <c r="H1" s="42"/>
-      <c r="I1" s="42"/>
-      <c r="J1" s="42"/>
-      <c r="K1" s="42"/>
-      <c r="L1" s="42"/>
-      <c r="M1" s="42"/>
-      <c r="N1" s="42"/>
-      <c r="O1" s="42"/>
-      <c r="P1" s="42"/>
-      <c r="Q1" s="42"/>
-      <c r="R1" s="42"/>
+      <c r="B1" s="40"/>
+      <c r="C1" s="40"/>
+      <c r="D1" s="40"/>
+      <c r="E1" s="40"/>
+      <c r="F1" s="40"/>
+      <c r="G1" s="40"/>
+      <c r="H1" s="40"/>
+      <c r="I1" s="40"/>
+      <c r="J1" s="40"/>
+      <c r="K1" s="40"/>
+      <c r="L1" s="40"/>
+      <c r="M1" s="40"/>
+      <c r="N1" s="40"/>
+      <c r="O1" s="40"/>
+      <c r="P1" s="40"/>
+      <c r="Q1" s="40"/>
+      <c r="R1" s="40"/>
     </row>
     <row r="2" spans="1:18">
       <c r="J2" s="31"/>
@@ -2734,6 +2894,165 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+  <dimension ref="A1:D13"/>
+  <sheetFormatPr defaultRowHeight="13.8"/>
+  <cols>
+    <col min="1" max="1" width="40" customWidth="1"/>
+    <col min="2" max="2" width="12" customWidth="1"/>
+    <col min="3" max="3" width="20" customWidth="1"/>
+    <col min="4" max="4" width="58" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="30" customHeight="1">
+      <c r="A1" s="47" t="s">
+        <v>190</v>
+      </c>
+      <c r="B1" s="47"/>
+      <c r="C1" s="47"/>
+      <c r="D1" s="47"/>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="B4" s="3">
+        <v>25</v>
+      </c>
+      <c r="C4" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="27.6">
+      <c r="A5" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="B5" s="3">
+        <v>25</v>
+      </c>
+      <c r="C5" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="B6" s="3">
+        <v>25</v>
+      </c>
+      <c r="C6" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="B7" s="3">
+        <v>25</v>
+      </c>
+      <c r="C7" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="B8" s="3">
+        <v>15</v>
+      </c>
+      <c r="C8" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="27.6">
+      <c r="A9" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="B9" s="3">
+        <v>10</v>
+      </c>
+      <c r="C9" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" s="7"/>
+      <c r="B10" s="7"/>
+      <c r="C10" s="7"/>
+      <c r="D10" s="7"/>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" s="30" t="s">
+        <v>206</v>
+      </c>
+      <c r="B11" s="30">
+        <v>125</v>
+      </c>
+      <c r="C11" s="7"/>
+      <c r="D11" s="7"/>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" s="7"/>
+      <c r="B12" s="7"/>
+      <c r="C12" s="7"/>
+      <c r="D12" s="7"/>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" s="49"/>
+      <c r="B13" s="49"/>
+      <c r="C13" s="49"/>
+      <c r="D13" s="49"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A13:D13"/>
+  </mergeCells>
+  <dataValidations count="1">
+    <dataValidation type="list" sqref="C4:C9" xr:uid="{00000000-0002-0000-0500-000000000000}">
+      <formula1>"Not Ready,Ready for Review,Complete"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:D13"/>
   <sheetFormatPr defaultRowHeight="13.8"/>
@@ -2745,12 +3064,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="30" customHeight="1">
-      <c r="A1" s="40" t="s">
+      <c r="A1" s="47" t="s">
         <v>207</v>
       </c>
-      <c r="B1" s="40"/>
-      <c r="C1" s="40"/>
-      <c r="D1" s="40"/>
+      <c r="B1" s="47"/>
+      <c r="C1" s="47"/>
+      <c r="D1" s="47"/>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
@@ -2873,12 +3192,12 @@
       <c r="D12" s="7"/>
     </row>
     <row r="13" spans="1:4">
-      <c r="A13" s="41" t="s">
+      <c r="A13" s="49" t="s">
         <v>219</v>
       </c>
-      <c r="B13" s="41"/>
-      <c r="C13" s="41"/>
-      <c r="D13" s="41"/>
+      <c r="B13" s="49"/>
+      <c r="C13" s="49"/>
+      <c r="D13" s="49"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -2887,6 +3206,167 @@
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="list" sqref="C4:C9" xr:uid="{00000000-0002-0000-0600-000000000000}">
+      <formula1>"Not Ready,Ready for Review,Complete"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E2A1FCF1-326B-4907-B522-C1578F400AED}">
+  <dimension ref="A1:D13"/>
+  <sheetFormatPr defaultRowHeight="13.8"/>
+  <cols>
+    <col min="1" max="1" width="40" customWidth="1"/>
+    <col min="2" max="2" width="12" customWidth="1"/>
+    <col min="3" max="3" width="20" customWidth="1"/>
+    <col min="4" max="4" width="58" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="30" customHeight="1">
+      <c r="A1" s="47" t="s">
+        <v>262</v>
+      </c>
+      <c r="B1" s="47"/>
+      <c r="C1" s="47"/>
+      <c r="D1" s="47"/>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="27.6">
+      <c r="A4" s="50" t="s">
+        <v>263</v>
+      </c>
+      <c r="B4" s="3">
+        <v>20</v>
+      </c>
+      <c r="C4" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="41.4">
+      <c r="A5" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="B5" s="3">
+        <v>30</v>
+      </c>
+      <c r="C5" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="27.6">
+      <c r="A6" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="B6" s="3">
+        <v>30</v>
+      </c>
+      <c r="C6" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="41.4">
+      <c r="A7" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="B7" s="3">
+        <v>20</v>
+      </c>
+      <c r="C7" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="41.4">
+      <c r="A8" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="B8" s="3">
+        <v>15</v>
+      </c>
+      <c r="C8" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="55.2">
+      <c r="A9" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="B9" s="3">
+        <v>10</v>
+      </c>
+      <c r="C9" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" s="7"/>
+      <c r="B10" s="7"/>
+      <c r="C10" s="7"/>
+      <c r="D10" s="7"/>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" s="30" t="s">
+        <v>206</v>
+      </c>
+      <c r="B11" s="30">
+        <v>125</v>
+      </c>
+      <c r="C11" s="7"/>
+      <c r="D11" s="7"/>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" s="7"/>
+      <c r="B12" s="7"/>
+      <c r="C12" s="7"/>
+      <c r="D12" s="7"/>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" s="49" t="s">
+        <v>219</v>
+      </c>
+      <c r="B13" s="49"/>
+      <c r="C13" s="49"/>
+      <c r="D13" s="49"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A13:D13"/>
+  </mergeCells>
+  <dataValidations count="1">
+    <dataValidation type="list" sqref="C4:C9" xr:uid="{5DCB1942-2CD7-4A5B-9DAE-EA32D2021DC4}">
       <formula1>"Not Ready,Ready for Review,Complete"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2914,26 +3394,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="30" customHeight="1">
-      <c r="A1" s="42" t="s">
+      <c r="A1" s="40" t="s">
         <v>88</v>
       </c>
-      <c r="B1" s="42"/>
-      <c r="C1" s="42"/>
-      <c r="D1" s="42"/>
-      <c r="E1" s="42"/>
-      <c r="F1" s="42"/>
-      <c r="G1" s="42"/>
-      <c r="H1" s="42"/>
-      <c r="I1" s="42"/>
-      <c r="J1" s="42"/>
-      <c r="K1" s="42"/>
-      <c r="L1" s="42"/>
-      <c r="M1" s="42"/>
-      <c r="N1" s="42"/>
-      <c r="O1" s="42"/>
-      <c r="P1" s="42"/>
-      <c r="Q1" s="42"/>
-      <c r="R1" s="42"/>
+      <c r="B1" s="40"/>
+      <c r="C1" s="40"/>
+      <c r="D1" s="40"/>
+      <c r="E1" s="40"/>
+      <c r="F1" s="40"/>
+      <c r="G1" s="40"/>
+      <c r="H1" s="40"/>
+      <c r="I1" s="40"/>
+      <c r="J1" s="40"/>
+      <c r="K1" s="40"/>
+      <c r="L1" s="40"/>
+      <c r="M1" s="40"/>
+      <c r="N1" s="40"/>
+      <c r="O1" s="40"/>
+      <c r="P1" s="40"/>
+      <c r="Q1" s="40"/>
+      <c r="R1" s="40"/>
     </row>
     <row r="2" spans="1:18">
       <c r="J2" s="7"/>
@@ -2950,120 +3430,120 @@
       <c r="A3" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="44" t="s">
+      <c r="B3" s="41" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="45"/>
-      <c r="D3" s="45"/>
-      <c r="E3" s="45"/>
-      <c r="F3" s="45"/>
-      <c r="G3" s="45"/>
-      <c r="H3" s="45"/>
-      <c r="I3" s="45"/>
-      <c r="J3" s="46"/>
-      <c r="K3" s="45"/>
-      <c r="L3" s="45"/>
-      <c r="M3" s="45"/>
-      <c r="N3" s="45"/>
-      <c r="O3" s="45"/>
-      <c r="P3" s="45"/>
-      <c r="Q3" s="45"/>
+      <c r="C3" s="42"/>
+      <c r="D3" s="42"/>
+      <c r="E3" s="42"/>
+      <c r="F3" s="42"/>
+      <c r="G3" s="42"/>
+      <c r="H3" s="42"/>
+      <c r="I3" s="42"/>
+      <c r="J3" s="43"/>
+      <c r="K3" s="42"/>
+      <c r="L3" s="42"/>
+      <c r="M3" s="42"/>
+      <c r="N3" s="42"/>
+      <c r="O3" s="42"/>
+      <c r="P3" s="42"/>
+      <c r="Q3" s="42"/>
       <c r="R3" s="7"/>
     </row>
     <row r="4" spans="1:18">
       <c r="A4" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="44" t="s">
+      <c r="B4" s="41" t="s">
         <v>89</v>
       </c>
-      <c r="C4" s="45"/>
-      <c r="D4" s="45"/>
-      <c r="E4" s="45"/>
-      <c r="F4" s="45"/>
-      <c r="G4" s="45"/>
-      <c r="H4" s="45"/>
-      <c r="I4" s="45"/>
-      <c r="J4" s="46"/>
-      <c r="K4" s="45"/>
-      <c r="L4" s="45"/>
-      <c r="M4" s="45"/>
-      <c r="N4" s="45"/>
-      <c r="O4" s="45"/>
-      <c r="P4" s="45"/>
-      <c r="Q4" s="45"/>
+      <c r="C4" s="42"/>
+      <c r="D4" s="42"/>
+      <c r="E4" s="42"/>
+      <c r="F4" s="42"/>
+      <c r="G4" s="42"/>
+      <c r="H4" s="42"/>
+      <c r="I4" s="42"/>
+      <c r="J4" s="43"/>
+      <c r="K4" s="42"/>
+      <c r="L4" s="42"/>
+      <c r="M4" s="42"/>
+      <c r="N4" s="42"/>
+      <c r="O4" s="42"/>
+      <c r="P4" s="42"/>
+      <c r="Q4" s="42"/>
       <c r="R4" s="7"/>
     </row>
     <row r="5" spans="1:18">
       <c r="A5" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="44" t="s">
+      <c r="B5" s="41" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="45"/>
-      <c r="D5" s="45"/>
-      <c r="E5" s="45"/>
-      <c r="F5" s="45"/>
-      <c r="G5" s="45"/>
-      <c r="H5" s="45"/>
-      <c r="I5" s="45"/>
-      <c r="J5" s="46"/>
-      <c r="K5" s="45"/>
-      <c r="L5" s="45"/>
-      <c r="M5" s="45"/>
-      <c r="N5" s="45"/>
-      <c r="O5" s="45"/>
-      <c r="P5" s="45"/>
-      <c r="Q5" s="45"/>
+      <c r="C5" s="42"/>
+      <c r="D5" s="42"/>
+      <c r="E5" s="42"/>
+      <c r="F5" s="42"/>
+      <c r="G5" s="42"/>
+      <c r="H5" s="42"/>
+      <c r="I5" s="42"/>
+      <c r="J5" s="43"/>
+      <c r="K5" s="42"/>
+      <c r="L5" s="42"/>
+      <c r="M5" s="42"/>
+      <c r="N5" s="42"/>
+      <c r="O5" s="42"/>
+      <c r="P5" s="42"/>
+      <c r="Q5" s="42"/>
       <c r="R5" s="7"/>
     </row>
     <row r="6" spans="1:18" ht="15" customHeight="1">
       <c r="A6" s="17" t="s">
         <v>90</v>
       </c>
-      <c r="B6" s="47" t="s">
+      <c r="B6" s="45" t="s">
         <v>91</v>
       </c>
-      <c r="C6" s="48"/>
-      <c r="D6" s="48"/>
-      <c r="E6" s="48"/>
-      <c r="F6" s="48"/>
-      <c r="G6" s="48"/>
-      <c r="H6" s="48"/>
-      <c r="I6" s="48"/>
-      <c r="J6" s="46"/>
-      <c r="K6" s="45"/>
-      <c r="L6" s="45"/>
-      <c r="M6" s="45"/>
-      <c r="N6" s="45"/>
-      <c r="O6" s="45"/>
-      <c r="P6" s="45"/>
-      <c r="Q6" s="45"/>
+      <c r="C6" s="46"/>
+      <c r="D6" s="46"/>
+      <c r="E6" s="46"/>
+      <c r="F6" s="46"/>
+      <c r="G6" s="46"/>
+      <c r="H6" s="46"/>
+      <c r="I6" s="46"/>
+      <c r="J6" s="43"/>
+      <c r="K6" s="42"/>
+      <c r="L6" s="42"/>
+      <c r="M6" s="42"/>
+      <c r="N6" s="42"/>
+      <c r="O6" s="42"/>
+      <c r="P6" s="42"/>
+      <c r="Q6" s="42"/>
       <c r="R6" s="7"/>
     </row>
     <row r="7" spans="1:18">
       <c r="A7" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="44" t="s">
+      <c r="B7" s="41" t="s">
         <v>92</v>
       </c>
-      <c r="C7" s="45"/>
-      <c r="D7" s="45"/>
-      <c r="E7" s="45"/>
-      <c r="F7" s="45"/>
-      <c r="G7" s="45"/>
-      <c r="H7" s="45"/>
-      <c r="I7" s="45"/>
-      <c r="J7" s="46"/>
-      <c r="K7" s="45"/>
-      <c r="L7" s="45"/>
-      <c r="M7" s="45"/>
-      <c r="N7" s="45"/>
-      <c r="O7" s="45"/>
-      <c r="P7" s="45"/>
-      <c r="Q7" s="45"/>
+      <c r="C7" s="42"/>
+      <c r="D7" s="42"/>
+      <c r="E7" s="42"/>
+      <c r="F7" s="42"/>
+      <c r="G7" s="42"/>
+      <c r="H7" s="42"/>
+      <c r="I7" s="42"/>
+      <c r="J7" s="43"/>
+      <c r="K7" s="42"/>
+      <c r="L7" s="42"/>
+      <c r="M7" s="42"/>
+      <c r="N7" s="42"/>
+      <c r="O7" s="42"/>
+      <c r="P7" s="42"/>
+      <c r="Q7" s="42"/>
       <c r="R7" s="7"/>
     </row>
     <row r="8" spans="1:18">
@@ -3514,26 +3994,26 @@
       <c r="R24" s="7"/>
     </row>
     <row r="25" spans="1:18" ht="14.4">
-      <c r="A25" s="43" t="s">
+      <c r="A25" s="44" t="s">
         <v>117</v>
       </c>
-      <c r="B25" s="43"/>
-      <c r="C25" s="43"/>
-      <c r="D25" s="43"/>
-      <c r="E25" s="43"/>
-      <c r="F25" s="43"/>
-      <c r="G25" s="43"/>
-      <c r="H25" s="43"/>
-      <c r="I25" s="43"/>
-      <c r="J25" s="43"/>
-      <c r="K25" s="43"/>
-      <c r="L25" s="43"/>
-      <c r="M25" s="43"/>
-      <c r="N25" s="43"/>
-      <c r="O25" s="43"/>
-      <c r="P25" s="43"/>
-      <c r="Q25" s="43"/>
-      <c r="R25" s="43"/>
+      <c r="B25" s="44"/>
+      <c r="C25" s="44"/>
+      <c r="D25" s="44"/>
+      <c r="E25" s="44"/>
+      <c r="F25" s="44"/>
+      <c r="G25" s="44"/>
+      <c r="H25" s="44"/>
+      <c r="I25" s="44"/>
+      <c r="J25" s="44"/>
+      <c r="K25" s="44"/>
+      <c r="L25" s="44"/>
+      <c r="M25" s="44"/>
+      <c r="N25" s="44"/>
+      <c r="O25" s="44"/>
+      <c r="P25" s="44"/>
+      <c r="Q25" s="44"/>
+      <c r="R25" s="44"/>
     </row>
     <row r="26" spans="1:18">
       <c r="J26" s="7"/>
@@ -4325,12 +4805,6 @@
     <row r="743" s="7" customFormat="1"/>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="A1:I1"/>
-    <mergeCell ref="J1:R1"/>
-    <mergeCell ref="B3:I3"/>
-    <mergeCell ref="J3:Q3"/>
-    <mergeCell ref="B4:I4"/>
-    <mergeCell ref="J4:Q4"/>
     <mergeCell ref="A25:I25"/>
     <mergeCell ref="J25:R25"/>
     <mergeCell ref="B5:I5"/>
@@ -4339,6 +4813,12 @@
     <mergeCell ref="J6:Q6"/>
     <mergeCell ref="B7:I7"/>
     <mergeCell ref="J7:Q7"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="J1:R1"/>
+    <mergeCell ref="B3:I3"/>
+    <mergeCell ref="J3:Q3"/>
+    <mergeCell ref="B4:I4"/>
+    <mergeCell ref="J4:Q4"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="list" sqref="G10:G20" xr:uid="{00000000-0002-0000-0100-000000000000}">
@@ -4372,26 +4852,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="30" customHeight="1">
-      <c r="A1" s="42" t="s">
+      <c r="A1" s="40" t="s">
         <v>220</v>
       </c>
-      <c r="B1" s="42"/>
-      <c r="C1" s="42"/>
-      <c r="D1" s="42"/>
-      <c r="E1" s="42"/>
-      <c r="F1" s="42"/>
-      <c r="G1" s="42"/>
-      <c r="H1" s="42"/>
-      <c r="I1" s="42"/>
-      <c r="J1" s="42"/>
-      <c r="K1" s="42"/>
-      <c r="L1" s="42"/>
-      <c r="M1" s="42"/>
-      <c r="N1" s="42"/>
-      <c r="O1" s="42"/>
-      <c r="P1" s="42"/>
-      <c r="Q1" s="42"/>
-      <c r="R1" s="42"/>
+      <c r="B1" s="40"/>
+      <c r="C1" s="40"/>
+      <c r="D1" s="40"/>
+      <c r="E1" s="40"/>
+      <c r="F1" s="40"/>
+      <c r="G1" s="40"/>
+      <c r="H1" s="40"/>
+      <c r="I1" s="40"/>
+      <c r="J1" s="40"/>
+      <c r="K1" s="40"/>
+      <c r="L1" s="40"/>
+      <c r="M1" s="40"/>
+      <c r="N1" s="40"/>
+      <c r="O1" s="40"/>
+      <c r="P1" s="40"/>
+      <c r="Q1" s="40"/>
+      <c r="R1" s="40"/>
     </row>
     <row r="2" spans="1:18">
       <c r="J2" s="7"/>
@@ -4408,116 +4888,116 @@
       <c r="A3" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="44" t="s">
+      <c r="B3" s="41" t="s">
         <v>221</v>
       </c>
-      <c r="C3" s="45"/>
-      <c r="D3" s="45"/>
-      <c r="E3" s="45"/>
-      <c r="F3" s="45"/>
-      <c r="G3" s="45"/>
-      <c r="H3" s="45"/>
-      <c r="I3" s="45"/>
-      <c r="J3" s="46"/>
-      <c r="K3" s="45"/>
-      <c r="L3" s="45"/>
-      <c r="M3" s="45"/>
-      <c r="N3" s="45"/>
-      <c r="O3" s="45"/>
-      <c r="P3" s="45"/>
-      <c r="Q3" s="45"/>
+      <c r="C3" s="42"/>
+      <c r="D3" s="42"/>
+      <c r="E3" s="42"/>
+      <c r="F3" s="42"/>
+      <c r="G3" s="42"/>
+      <c r="H3" s="42"/>
+      <c r="I3" s="42"/>
+      <c r="J3" s="43"/>
+      <c r="K3" s="42"/>
+      <c r="L3" s="42"/>
+      <c r="M3" s="42"/>
+      <c r="N3" s="42"/>
+      <c r="O3" s="42"/>
+      <c r="P3" s="42"/>
+      <c r="Q3" s="42"/>
       <c r="R3" s="7"/>
     </row>
     <row r="4" spans="1:18">
       <c r="A4" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="44" t="s">
+      <c r="B4" s="41" t="s">
         <v>222</v>
       </c>
-      <c r="C4" s="45"/>
-      <c r="D4" s="45"/>
-      <c r="E4" s="45"/>
-      <c r="F4" s="45"/>
-      <c r="G4" s="45"/>
-      <c r="H4" s="45"/>
-      <c r="I4" s="45"/>
-      <c r="J4" s="46"/>
-      <c r="K4" s="45"/>
-      <c r="L4" s="45"/>
-      <c r="M4" s="45"/>
-      <c r="N4" s="45"/>
-      <c r="O4" s="45"/>
-      <c r="P4" s="45"/>
-      <c r="Q4" s="45"/>
+      <c r="C4" s="42"/>
+      <c r="D4" s="42"/>
+      <c r="E4" s="42"/>
+      <c r="F4" s="42"/>
+      <c r="G4" s="42"/>
+      <c r="H4" s="42"/>
+      <c r="I4" s="42"/>
+      <c r="J4" s="43"/>
+      <c r="K4" s="42"/>
+      <c r="L4" s="42"/>
+      <c r="M4" s="42"/>
+      <c r="N4" s="42"/>
+      <c r="O4" s="42"/>
+      <c r="P4" s="42"/>
+      <c r="Q4" s="42"/>
       <c r="R4" s="7"/>
     </row>
     <row r="5" spans="1:18">
       <c r="A5" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="44" t="s">
+      <c r="B5" s="41" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="45"/>
-      <c r="D5" s="45"/>
-      <c r="E5" s="45"/>
-      <c r="F5" s="45"/>
-      <c r="G5" s="45"/>
-      <c r="H5" s="45"/>
-      <c r="I5" s="45"/>
-      <c r="J5" s="46"/>
-      <c r="K5" s="45"/>
-      <c r="L5" s="45"/>
-      <c r="M5" s="45"/>
-      <c r="N5" s="45"/>
-      <c r="O5" s="45"/>
-      <c r="P5" s="45"/>
-      <c r="Q5" s="45"/>
+      <c r="C5" s="42"/>
+      <c r="D5" s="42"/>
+      <c r="E5" s="42"/>
+      <c r="F5" s="42"/>
+      <c r="G5" s="42"/>
+      <c r="H5" s="42"/>
+      <c r="I5" s="42"/>
+      <c r="J5" s="43"/>
+      <c r="K5" s="42"/>
+      <c r="L5" s="42"/>
+      <c r="M5" s="42"/>
+      <c r="N5" s="42"/>
+      <c r="O5" s="42"/>
+      <c r="P5" s="42"/>
+      <c r="Q5" s="42"/>
       <c r="R5" s="7"/>
     </row>
     <row r="6" spans="1:18" ht="15" customHeight="1">
       <c r="A6" s="17" t="s">
         <v>90</v>
       </c>
-      <c r="B6" s="47"/>
-      <c r="C6" s="48"/>
-      <c r="D6" s="48"/>
-      <c r="E6" s="48"/>
-      <c r="F6" s="48"/>
-      <c r="G6" s="48"/>
-      <c r="H6" s="48"/>
-      <c r="I6" s="48"/>
-      <c r="J6" s="46"/>
-      <c r="K6" s="45"/>
-      <c r="L6" s="45"/>
-      <c r="M6" s="45"/>
-      <c r="N6" s="45"/>
-      <c r="O6" s="45"/>
-      <c r="P6" s="45"/>
-      <c r="Q6" s="45"/>
+      <c r="B6" s="45"/>
+      <c r="C6" s="46"/>
+      <c r="D6" s="46"/>
+      <c r="E6" s="46"/>
+      <c r="F6" s="46"/>
+      <c r="G6" s="46"/>
+      <c r="H6" s="46"/>
+      <c r="I6" s="46"/>
+      <c r="J6" s="43"/>
+      <c r="K6" s="42"/>
+      <c r="L6" s="42"/>
+      <c r="M6" s="42"/>
+      <c r="N6" s="42"/>
+      <c r="O6" s="42"/>
+      <c r="P6" s="42"/>
+      <c r="Q6" s="42"/>
       <c r="R6" s="7"/>
     </row>
     <row r="7" spans="1:18">
       <c r="A7" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="44"/>
-      <c r="C7" s="45"/>
-      <c r="D7" s="45"/>
-      <c r="E7" s="45"/>
-      <c r="F7" s="45"/>
-      <c r="G7" s="45"/>
-      <c r="H7" s="45"/>
-      <c r="I7" s="45"/>
-      <c r="J7" s="46"/>
-      <c r="K7" s="45"/>
-      <c r="L7" s="45"/>
-      <c r="M7" s="45"/>
-      <c r="N7" s="45"/>
-      <c r="O7" s="45"/>
-      <c r="P7" s="45"/>
-      <c r="Q7" s="45"/>
+      <c r="B7" s="41"/>
+      <c r="C7" s="42"/>
+      <c r="D7" s="42"/>
+      <c r="E7" s="42"/>
+      <c r="F7" s="42"/>
+      <c r="G7" s="42"/>
+      <c r="H7" s="42"/>
+      <c r="I7" s="42"/>
+      <c r="J7" s="43"/>
+      <c r="K7" s="42"/>
+      <c r="L7" s="42"/>
+      <c r="M7" s="42"/>
+      <c r="N7" s="42"/>
+      <c r="O7" s="42"/>
+      <c r="P7" s="42"/>
+      <c r="Q7" s="42"/>
       <c r="R7" s="7"/>
     </row>
     <row r="8" spans="1:18">
@@ -4885,26 +5365,26 @@
       <c r="R24" s="7"/>
     </row>
     <row r="25" spans="1:18" ht="14.4">
-      <c r="A25" s="43" t="s">
+      <c r="A25" s="44" t="s">
         <v>227</v>
       </c>
-      <c r="B25" s="43"/>
-      <c r="C25" s="43"/>
-      <c r="D25" s="43"/>
-      <c r="E25" s="43"/>
-      <c r="F25" s="43"/>
-      <c r="G25" s="43"/>
-      <c r="H25" s="43"/>
-      <c r="I25" s="43"/>
-      <c r="J25" s="43"/>
-      <c r="K25" s="43"/>
-      <c r="L25" s="43"/>
-      <c r="M25" s="43"/>
-      <c r="N25" s="43"/>
-      <c r="O25" s="43"/>
-      <c r="P25" s="43"/>
-      <c r="Q25" s="43"/>
-      <c r="R25" s="43"/>
+      <c r="B25" s="44"/>
+      <c r="C25" s="44"/>
+      <c r="D25" s="44"/>
+      <c r="E25" s="44"/>
+      <c r="F25" s="44"/>
+      <c r="G25" s="44"/>
+      <c r="H25" s="44"/>
+      <c r="I25" s="44"/>
+      <c r="J25" s="44"/>
+      <c r="K25" s="44"/>
+      <c r="L25" s="44"/>
+      <c r="M25" s="44"/>
+      <c r="N25" s="44"/>
+      <c r="O25" s="44"/>
+      <c r="P25" s="44"/>
+      <c r="Q25" s="44"/>
+      <c r="R25" s="44"/>
     </row>
     <row r="26" spans="1:18">
       <c r="J26" s="7"/>
@@ -5696,12 +6176,6 @@
     <row r="743" s="7" customFormat="1"/>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="A1:I1"/>
-    <mergeCell ref="J1:R1"/>
-    <mergeCell ref="B3:I3"/>
-    <mergeCell ref="J3:Q3"/>
-    <mergeCell ref="B4:I4"/>
-    <mergeCell ref="J4:Q4"/>
     <mergeCell ref="A25:I25"/>
     <mergeCell ref="J25:R25"/>
     <mergeCell ref="B5:I5"/>
@@ -5710,6 +6184,12 @@
     <mergeCell ref="J6:Q6"/>
     <mergeCell ref="B7:I7"/>
     <mergeCell ref="J7:Q7"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="J1:R1"/>
+    <mergeCell ref="B3:I3"/>
+    <mergeCell ref="J3:Q3"/>
+    <mergeCell ref="B4:I4"/>
+    <mergeCell ref="J4:Q4"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="list" sqref="D10:D20" xr:uid="{6618791A-2420-4F4B-8340-167A339F0717}">
@@ -5720,6 +6200,7 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -5738,15 +6219,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="30" customHeight="1">
-      <c r="A1" s="40" t="s">
+      <c r="A1" s="47" t="s">
         <v>118</v>
       </c>
-      <c r="B1" s="40"/>
-      <c r="C1" s="40"/>
-      <c r="D1" s="40"/>
-      <c r="E1" s="40"/>
-      <c r="F1" s="40"/>
-      <c r="G1" s="40"/>
+      <c r="B1" s="47"/>
+      <c r="C1" s="47"/>
+      <c r="D1" s="47"/>
+      <c r="E1" s="47"/>
+      <c r="F1" s="47"/>
+      <c r="G1" s="47"/>
     </row>
     <row r="3" spans="1:7">
       <c r="A3" s="1" t="s">
@@ -6059,15 +6540,15 @@
       </c>
     </row>
     <row r="27" spans="1:7" ht="14.4">
-      <c r="A27" s="49" t="s">
+      <c r="A27" s="48" t="s">
         <v>137</v>
       </c>
-      <c r="B27" s="49"/>
-      <c r="C27" s="49"/>
-      <c r="D27" s="49"/>
-      <c r="E27" s="49"/>
-      <c r="F27" s="49"/>
-      <c r="G27" s="49"/>
+      <c r="B27" s="48"/>
+      <c r="C27" s="48"/>
+      <c r="D27" s="48"/>
+      <c r="E27" s="48"/>
+      <c r="F27" s="48"/>
+      <c r="G27" s="48"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -6101,15 +6582,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="30" customHeight="1">
-      <c r="A1" s="40" t="s">
+      <c r="A1" s="47" t="s">
         <v>138</v>
       </c>
-      <c r="B1" s="40"/>
-      <c r="C1" s="40"/>
-      <c r="D1" s="40"/>
-      <c r="E1" s="40"/>
-      <c r="F1" s="40"/>
-      <c r="G1" s="40"/>
+      <c r="B1" s="47"/>
+      <c r="C1" s="47"/>
+      <c r="D1" s="47"/>
+      <c r="E1" s="47"/>
+      <c r="F1" s="47"/>
+      <c r="G1" s="47"/>
     </row>
     <row r="3" spans="1:7">
       <c r="A3" s="1" t="s">
@@ -6533,15 +7014,15 @@
       </c>
     </row>
     <row r="27" spans="1:7" ht="14.4">
-      <c r="A27" s="49" t="s">
+      <c r="A27" s="48" t="s">
         <v>167</v>
       </c>
-      <c r="B27" s="49"/>
-      <c r="C27" s="49"/>
-      <c r="D27" s="49"/>
-      <c r="E27" s="49"/>
-      <c r="F27" s="49"/>
-      <c r="G27" s="49"/>
+      <c r="B27" s="48"/>
+      <c r="C27" s="48"/>
+      <c r="D27" s="48"/>
+      <c r="E27" s="48"/>
+      <c r="F27" s="48"/>
+      <c r="G27" s="48"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -6576,15 +7057,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="30" customHeight="1">
-      <c r="A1" s="40" t="s">
+      <c r="A1" s="47" t="s">
         <v>229</v>
       </c>
-      <c r="B1" s="40"/>
-      <c r="C1" s="40"/>
-      <c r="D1" s="40"/>
-      <c r="E1" s="40"/>
-      <c r="F1" s="40"/>
-      <c r="G1" s="40"/>
+      <c r="B1" s="47"/>
+      <c r="C1" s="47"/>
+      <c r="D1" s="47"/>
+      <c r="E1" s="47"/>
+      <c r="F1" s="47"/>
+      <c r="G1" s="47"/>
     </row>
     <row r="3" spans="1:7">
       <c r="A3" s="1" t="s">
@@ -6908,15 +7389,15 @@
       </c>
     </row>
     <row r="27" spans="1:7" ht="14.4">
-      <c r="A27" s="49" t="s">
+      <c r="A27" s="48" t="s">
         <v>167</v>
       </c>
-      <c r="B27" s="49"/>
-      <c r="C27" s="49"/>
-      <c r="D27" s="49"/>
-      <c r="E27" s="49"/>
-      <c r="F27" s="49"/>
-      <c r="G27" s="49"/>
+      <c r="B27" s="48"/>
+      <c r="C27" s="48"/>
+      <c r="D27" s="48"/>
+      <c r="E27" s="48"/>
+      <c r="F27" s="48"/>
+      <c r="G27" s="48"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -6950,15 +7431,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="30" customHeight="1">
-      <c r="A1" s="40" t="s">
+      <c r="A1" s="47" t="s">
         <v>168</v>
       </c>
-      <c r="B1" s="40"/>
-      <c r="C1" s="40"/>
-      <c r="D1" s="40"/>
-      <c r="E1" s="40"/>
-      <c r="F1" s="40"/>
-      <c r="G1" s="40"/>
+      <c r="B1" s="47"/>
+      <c r="C1" s="47"/>
+      <c r="D1" s="47"/>
+      <c r="E1" s="47"/>
+      <c r="F1" s="47"/>
+      <c r="G1" s="47"/>
     </row>
     <row r="3" spans="1:7">
       <c r="A3" s="1" t="s">
@@ -7090,15 +7571,15 @@
       <c r="G9" s="21"/>
     </row>
     <row r="11" spans="1:7" ht="14.4">
-      <c r="A11" s="43" t="s">
+      <c r="A11" s="44" t="s">
         <v>189</v>
       </c>
-      <c r="B11" s="43"/>
-      <c r="C11" s="43"/>
-      <c r="D11" s="43"/>
-      <c r="E11" s="43"/>
-      <c r="F11" s="43"/>
-      <c r="G11" s="43"/>
+      <c r="B11" s="44"/>
+      <c r="C11" s="44"/>
+      <c r="D11" s="44"/>
+      <c r="E11" s="44"/>
+      <c r="F11" s="44"/>
+      <c r="G11" s="44"/>
     </row>
     <row r="17" spans="5:5">
       <c r="E17" s="16"/>
@@ -7132,15 +7613,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="30" customHeight="1">
-      <c r="A1" s="40" t="s">
+      <c r="A1" s="47" t="s">
         <v>235</v>
       </c>
-      <c r="B1" s="40"/>
-      <c r="C1" s="40"/>
-      <c r="D1" s="40"/>
-      <c r="E1" s="40"/>
-      <c r="F1" s="40"/>
-      <c r="G1" s="40"/>
+      <c r="B1" s="47"/>
+      <c r="C1" s="47"/>
+      <c r="D1" s="47"/>
+      <c r="E1" s="47"/>
+      <c r="F1" s="47"/>
+      <c r="G1" s="47"/>
     </row>
     <row r="3" spans="1:7">
       <c r="A3" s="1" t="s">
@@ -7167,16 +7648,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4" s="19">
-        <v>46268</v>
+        <v>46273</v>
       </c>
       <c r="B4" s="26" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="C4" s="21" t="s">
         <v>176</v>
       </c>
       <c r="D4" s="21" t="s">
-        <v>177</v>
+        <v>254</v>
       </c>
       <c r="E4" s="21" t="s">
         <v>178</v>
@@ -7186,16 +7667,16 @@
     </row>
     <row r="5" spans="1:7" ht="41.4">
       <c r="A5" s="19">
-        <v>46270</v>
+        <v>46274</v>
       </c>
       <c r="B5" s="29" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="C5" s="24" t="s">
         <v>176</v>
       </c>
       <c r="D5" s="29" t="s">
-        <v>177</v>
+        <v>255</v>
       </c>
       <c r="E5" s="21" t="s">
         <v>179</v>
@@ -7205,16 +7686,16 @@
     </row>
     <row r="6" spans="1:7" ht="41.4">
       <c r="A6" s="19">
-        <v>46271</v>
+        <v>46275</v>
       </c>
       <c r="B6" s="29" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="C6" s="24" t="s">
         <v>176</v>
       </c>
       <c r="D6" s="24" t="s">
-        <v>177</v>
+        <v>256</v>
       </c>
       <c r="E6" s="24" t="s">
         <v>180</v>
@@ -7224,7 +7705,7 @@
     </row>
     <row r="7" spans="1:7" ht="27.6">
       <c r="A7" s="19">
-        <v>46270</v>
+        <v>46276</v>
       </c>
       <c r="B7" s="26" t="s">
         <v>181</v>
@@ -7233,7 +7714,7 @@
         <v>182</v>
       </c>
       <c r="D7" s="21" t="s">
-        <v>183</v>
+        <v>257</v>
       </c>
       <c r="E7" s="21" t="s">
         <v>184</v>
@@ -7242,9 +7723,11 @@
       <c r="G7" s="21"/>
     </row>
     <row r="8" spans="1:7" ht="27.6">
-      <c r="A8" s="19"/>
+      <c r="A8" s="19">
+        <v>46279</v>
+      </c>
       <c r="B8" s="26" t="s">
-        <v>185</v>
+        <v>258</v>
       </c>
       <c r="C8" s="21" t="s">
         <v>134</v>
@@ -7272,15 +7755,15 @@
       <c r="G9" s="21"/>
     </row>
     <row r="11" spans="1:7" ht="14.4">
-      <c r="A11" s="43" t="s">
+      <c r="A11" s="44" t="s">
         <v>189</v>
       </c>
-      <c r="B11" s="43"/>
-      <c r="C11" s="43"/>
-      <c r="D11" s="43"/>
-      <c r="E11" s="43"/>
-      <c r="F11" s="43"/>
-      <c r="G11" s="43"/>
+      <c r="B11" s="44"/>
+      <c r="C11" s="44"/>
+      <c r="D11" s="44"/>
+      <c r="E11" s="44"/>
+      <c r="F11" s="44"/>
+      <c r="G11" s="44"/>
     </row>
     <row r="17" spans="5:5">
       <c r="E17" s="16"/>
@@ -7300,158 +7783,169 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:D13"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CEDD1FD8-3234-4A2D-8F9E-152FEC63B149}">
+  <dimension ref="A1:G17"/>
   <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="1" width="40" customWidth="1"/>
-    <col min="2" max="2" width="12" customWidth="1"/>
-    <col min="3" max="3" width="20" customWidth="1"/>
-    <col min="4" max="4" width="58" customWidth="1"/>
+    <col min="1" max="1" width="14" customWidth="1"/>
+    <col min="2" max="2" width="22" customWidth="1"/>
+    <col min="3" max="3" width="32" customWidth="1"/>
+    <col min="4" max="4" width="30" customWidth="1"/>
+    <col min="5" max="5" width="46" customWidth="1"/>
+    <col min="6" max="6" width="22" customWidth="1"/>
+    <col min="7" max="7" width="35" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="30" customHeight="1">
-      <c r="A1" s="40" t="s">
-        <v>190</v>
-      </c>
-      <c r="B1" s="40"/>
-      <c r="C1" s="40"/>
-      <c r="D1" s="40"/>
-    </row>
-    <row r="3" spans="1:4">
+    <row r="1" spans="1:7" ht="30" customHeight="1">
+      <c r="A1" s="47" t="s">
+        <v>259</v>
+      </c>
+      <c r="B1" s="47"/>
+      <c r="C1" s="47"/>
+      <c r="D1" s="47"/>
+      <c r="E1" s="47"/>
+      <c r="F1" s="47"/>
+      <c r="G1" s="47"/>
+    </row>
+    <row r="3" spans="1:7">
       <c r="A3" s="1" t="s">
-        <v>191</v>
+        <v>119</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>192</v>
+        <v>169</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>17</v>
+        <v>170</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
-      <c r="A4" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="B4" s="3">
-        <v>25</v>
+        <v>171</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" s="19">
+        <v>46280</v>
+      </c>
+      <c r="B4" s="26" t="s">
+        <v>181</v>
       </c>
       <c r="C4" s="21" t="s">
-        <v>25</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" ht="27.6">
-      <c r="A5" s="3" t="s">
-        <v>196</v>
-      </c>
-      <c r="B5" s="3">
-        <v>25</v>
-      </c>
-      <c r="C5" s="21" t="s">
-        <v>25</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
-      <c r="A6" s="3" t="s">
-        <v>198</v>
-      </c>
-      <c r="B6" s="3">
-        <v>25</v>
-      </c>
-      <c r="C6" s="21" t="s">
-        <v>25</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4">
-      <c r="A7" s="3" t="s">
-        <v>200</v>
-      </c>
-      <c r="B7" s="3">
-        <v>25</v>
+        <v>176</v>
+      </c>
+      <c r="D4" s="21" t="s">
+        <v>254</v>
+      </c>
+      <c r="E4" s="21" t="s">
+        <v>178</v>
+      </c>
+      <c r="F4" s="21"/>
+      <c r="G4" s="21"/>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" s="19">
+        <v>46281</v>
+      </c>
+      <c r="B5" s="29" t="s">
+        <v>181</v>
+      </c>
+      <c r="C5" s="24" t="s">
+        <v>176</v>
+      </c>
+      <c r="D5" s="29" t="s">
+        <v>255</v>
+      </c>
+      <c r="E5" s="21" t="s">
+        <v>261</v>
+      </c>
+      <c r="F5" s="21"/>
+      <c r="G5" s="21"/>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6" s="19">
+        <v>46282</v>
+      </c>
+      <c r="B6" s="29" t="s">
+        <v>181</v>
+      </c>
+      <c r="C6" s="24" t="s">
+        <v>176</v>
+      </c>
+      <c r="D6" s="24" t="s">
+        <v>256</v>
+      </c>
+      <c r="E6" s="24" t="s">
+        <v>272</v>
+      </c>
+      <c r="F6" s="21"/>
+      <c r="G6" s="21"/>
+    </row>
+    <row r="7" spans="1:7" ht="27.6">
+      <c r="A7" s="19">
+        <v>46285</v>
+      </c>
+      <c r="B7" s="26" t="s">
+        <v>181</v>
       </c>
       <c r="C7" s="21" t="s">
-        <v>25</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4">
-      <c r="A8" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="B8" s="3">
-        <v>15</v>
-      </c>
-      <c r="C8" s="21" t="s">
-        <v>25</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" ht="27.6">
-      <c r="A9" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="B9" s="3">
-        <v>10</v>
-      </c>
-      <c r="C9" s="21" t="s">
-        <v>25</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4">
-      <c r="A10" s="7"/>
-      <c r="B10" s="7"/>
-      <c r="C10" s="7"/>
-      <c r="D10" s="7"/>
-    </row>
-    <row r="11" spans="1:4">
-      <c r="A11" s="30" t="s">
-        <v>206</v>
-      </c>
-      <c r="B11" s="30">
-        <v>125</v>
-      </c>
-      <c r="C11" s="7"/>
-      <c r="D11" s="7"/>
-    </row>
-    <row r="12" spans="1:4">
-      <c r="A12" s="7"/>
-      <c r="B12" s="7"/>
-      <c r="C12" s="7"/>
-      <c r="D12" s="7"/>
-    </row>
-    <row r="13" spans="1:4">
-      <c r="A13" s="41"/>
-      <c r="B13" s="41"/>
-      <c r="C13" s="41"/>
-      <c r="D13" s="41"/>
+        <v>176</v>
+      </c>
+      <c r="D7" s="21" t="s">
+        <v>257</v>
+      </c>
+      <c r="E7" s="21" t="s">
+        <v>260</v>
+      </c>
+      <c r="F7" s="21"/>
+      <c r="G7" s="21"/>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8" s="19"/>
+      <c r="B8" s="26"/>
+      <c r="C8" s="21"/>
+      <c r="D8" s="21"/>
+      <c r="E8" s="21"/>
+      <c r="F8" s="21"/>
+      <c r="G8" s="21"/>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9" s="19"/>
+      <c r="B9" s="26"/>
+      <c r="C9" s="21"/>
+      <c r="D9" s="21"/>
+      <c r="E9" s="21"/>
+      <c r="F9" s="21"/>
+      <c r="G9" s="21"/>
+    </row>
+    <row r="11" spans="1:7" ht="14.4">
+      <c r="A11" s="44" t="s">
+        <v>189</v>
+      </c>
+      <c r="B11" s="44"/>
+      <c r="C11" s="44"/>
+      <c r="D11" s="44"/>
+      <c r="E11" s="44"/>
+      <c r="F11" s="44"/>
+      <c r="G11" s="44"/>
+    </row>
+    <row r="17" spans="5:5">
+      <c r="E17" s="16"/>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A13:D13"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A11:G11"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation type="list" sqref="C4:C9" xr:uid="{00000000-0002-0000-0500-000000000000}">
-      <formula1>"Not Ready,Ready for Review,Complete"</formula1>
+    <dataValidation type="list" sqref="B4:B9" xr:uid="{CDFB1E5E-898E-447A-86D4-EB2318762C35}">
+      <formula1>"CTU Discussion Board,Email,Teams/Zoom,Phone,Shared Document,Other"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
